--- a/Angebotsdaten.xlsx
+++ b/Angebotsdaten.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://springernature-my.sharepoint.com/personal/mss4379_springernature_com/Documents/SM Onkologie + Diabetologie/Angebotsvorlagen/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2796" documentId="13_ncr:1_{16275085-EE8E-A342-9A17-24AB12538757}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{347E3970-F2FE-488B-8C6F-BF5667978178}"/>
+  <xr:revisionPtr revIDLastSave="2802" documentId="13_ncr:1_{16275085-EE8E-A342-9A17-24AB12538757}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D905F175-7A82-47CB-B21F-C686005511AB}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15270" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10828" uniqueCount="692">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10831" uniqueCount="696">
   <si>
     <t>Wird in der Vorlage über »Daten laden« eingelesen. Der Dateiname ist frei wählbar;</t>
   </si>
@@ -2266,6 +2266,19 @@
   <si>
     <t>TOP-THEMA: Liquid Biopsy: Vom Monitoring zur Therapieentscheidung?
 SCHWERPUNKT-THEMA: Multimodale Ansätze beim Prostatakarzinom</t>
+  </si>
+  <si>
+    <t>TOP-THEMA: Myeloproliferative Neoplasien (MPN) – Therapien im Wandel (mit Schwerpunkt auf PV und ET)
+SCHWERPUNKT-THEMA: Nierenzellkarzinom – neue Therapien im Blick</t>
+  </si>
+  <si>
+    <t>ASCO Annual Meeting (Bericht), 04.–08.06.2027, Chicago</t>
+  </si>
+  <si>
+    <t>EHA Congress (Bericht), 13.–17.06.2027, Barcelona</t>
+  </si>
+  <si>
+    <t>DGHO Jahrestagung (Bericht), 08.11.−11.10.2027, Leipzig</t>
   </si>
 </sst>
 </file>
@@ -45995,7 +46008,7 @@
         <v>335</v>
       </c>
     </row>
-    <row r="20" spans="1:10" customFormat="1" ht="63.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:10" customFormat="1" ht="51" hidden="1" x14ac:dyDescent="0.25">
       <c r="A20" s="4">
         <v>2026</v>
       </c>
@@ -48514,7 +48527,7 @@
         <v>259</v>
       </c>
       <c r="I103" s="11" t="s">
-        <v>438</v>
+        <v>692</v>
       </c>
       <c r="J103" s="7" t="s">
         <v>477</v>
@@ -48545,6 +48558,9 @@
       <c r="I104" s="11" t="s">
         <v>686</v>
       </c>
+      <c r="J104" s="7" t="s">
+        <v>693</v>
+      </c>
     </row>
     <row r="105" spans="1:10" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A105" s="4">
@@ -48571,6 +48587,9 @@
       <c r="I105" s="11" t="s">
         <v>687</v>
       </c>
+      <c r="J105" s="7" t="s">
+        <v>694</v>
+      </c>
     </row>
     <row r="106" spans="1:10" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A106" s="4">
@@ -48651,6 +48670,9 @@
       </c>
       <c r="I108" s="11" t="s">
         <v>690</v>
+      </c>
+      <c r="J108" s="7" t="s">
+        <v>695</v>
       </c>
     </row>
     <row r="109" spans="1:10" ht="25.5" x14ac:dyDescent="0.2">

--- a/Angebotsdaten.xlsx
+++ b/Angebotsdaten.xlsx
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11134" uniqueCount="703">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11135" uniqueCount="704">
   <si>
     <t>Wird in der Vorlage über »Daten laden« eingelesen. Der Dateiname ist frei wählbar;</t>
   </si>
@@ -2308,6 +2308,9 @@
   <si>
     <t>Gehirn
 CME: Übergewicht und Adipositas im Kindes- und Jugendalter</t>
+  </si>
+  <si>
+    <t>Seiten-Äquivalent</t>
   </si>
 </sst>
 </file>
@@ -2901,7 +2904,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:K1449"/>
+  <dimension ref="A1:L1449"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10" style="16" customWidth="1"/>
@@ -2915,9 +2918,10 @@
     <col min="9" max="9" width="10.85546875" style="16" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="16" style="22" customWidth="1"/>
     <col min="11" max="11" width="12.85546875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="17.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:12" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
         <v>8</v>
       </c>
@@ -2950,6 +2954,9 @@
       </c>
       <c r="K1" s="3" t="s">
         <v>673</v>
+      </c>
+      <c r="L1" s="3" t="s">
+        <v>703</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.25">

--- a/Angebotsdaten.xlsx
+++ b/Angebotsdaten.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mss4379\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{160D184F-FC11-473C-A2B8-94868699121C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9C8E590-B5DF-4546-8119-2B1EB8949B51}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="25080" yWindow="-150" windowWidth="25440" windowHeight="15270" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25318,7 +25318,7 @@
         <v>25</v>
       </c>
       <c r="F690" s="9">
-        <v>5820</v>
+        <v>5770</v>
       </c>
       <c r="G690" s="9"/>
       <c r="H690" s="6" t="s">

--- a/Angebotsdaten.xlsx
+++ b/Angebotsdaten.xlsx
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11135" uniqueCount="704">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11136" uniqueCount="705">
   <si>
     <t>Wird in der Vorlage über »Daten laden« eingelesen. Der Dateiname ist frei wählbar;</t>
   </si>
@@ -1949,13 +1949,13 @@
     <t>19.10.</t>
   </si>
   <si>
-    <t>04.12.25</t>
-  </si>
-  <si>
-    <t>08.12.25</t>
-  </si>
-  <si>
-    <t>17.12.25</t>
+    <t>04.12.2025</t>
+  </si>
+  <si>
+    <t>08.12.2025</t>
+  </si>
+  <si>
+    <t>17.12.2025</t>
   </si>
   <si>
     <t>11.02.</t>
@@ -2311,6 +2311,9 @@
   </si>
   <si>
     <t>Seiten-Äquivalent</t>
+  </si>
+  <si>
+    <t>22.12.2026</t>
   </si>
 </sst>
 </file>
@@ -52394,8 +52397,8 @@
       <c r="E211" s="21" t="s">
         <v>225</v>
       </c>
-      <c r="F211" s="21">
-        <v>46378</v>
+      <c r="F211" s="21" t="s">
+        <v>704</v>
       </c>
       <c r="G211" s="21" t="s">
         <v>468</v>

--- a/Angebotsdaten.xlsx
+++ b/Angebotsdaten.xlsx
@@ -453,14 +453,14 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Gepflegt wird in der Preispflege:</t>
+          <t>Gepflegt wird in der Datenpflege:</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t xml:space="preserve">   https://barings1995.github.io/angebotswerkzeuge/Preispflege.html</t>
+          <t xml:space="preserve">   https://barings1995.github.io/angebotswerkzeuge/Datenpflege.html</t>
         </is>
       </c>
     </row>

--- a/Angebotsdaten.xlsx
+++ b/Angebotsdaten.xlsx
@@ -70844,7 +70844,10 @@
       </c>
       <c r="J170" t="inlineStr">
         <is>
-          <t>DGP Kongress (Auslage), 03.03.–06.03.2027, Köln</t>
+          <t>DGP Kongress (Auslage), 03.03.–06.03.2027, Köln
+23. AIO-Herbstkongress 2026 (Bericht)
+68th ASH Annual Meeting and Exposition 2026 (ASH 2026) (Bericht)
+48th Annual San Antonio Breast Cancer Symposium (SABCS 2026)</t>
         </is>
       </c>
     </row>
@@ -71304,7 +71307,10 @@
       </c>
       <c r="J180" t="inlineStr">
         <is>
-          <t>DGP Kongress (Auslage), 03.03.–06.03.2027, Köln</t>
+          <t>DGP Kongress (Auslage), 03.03.–06.03.2027, Köln
+23. AIO-Herbstkongress 2026 (Bericht)
+68th ASH Annual Meeting and Exposition 2026 (ASH 2026) (Bericht)
+48th Annual San Antonio Breast Cancer Symposium (SABCS 2026)</t>
         </is>
       </c>
     </row>
@@ -71570,7 +71576,9 @@
       </c>
       <c r="J186" t="inlineStr">
         <is>
-          <t>DGP Kongress (Auslage), 03.03.–06.03.2027, Köln</t>
+          <t>DGP Kongress (Auslage), 03.03.–06.03.2027, Köln
+68th ASH Annual Meeting and Exposition 2026 (ASH 2026) (Bericht)
+48th Annual San Antonio Breast Cancer Symposium (SABCS 2026)</t>
         </is>
       </c>
     </row>

--- a/Angebotsdaten.xlsx
+++ b/Angebotsdaten.xlsx
@@ -65147,7 +65147,7 @@
         <is>
           <t>GTH Jahrestagung (Auslage), 17.02.−20.02.2026, Bonn
 DKK (Auslage), 18.02.−21.02.2026, Berlin
-ELN-/KNL-Symposium (Auslage), 03.03.2026
+ELN-/KNL-Symposium (Auslage), 03.03.2026, Mannheim
 DGHO Frühjahrstagung (Auslage), 13.03.2026, Berlin
 DGP Kongress (Auslage), 18.03.−21.03.2026, München
 AIO-Herbstkongress (Bericht), 20.11.−22.11.2025, Berlin
@@ -70895,6 +70895,13 @@
           <t>Gastroonkologie</t>
         </is>
       </c>
+      <c r="J171" t="inlineStr">
+        <is>
+          <t>ASCO-GI Gastrointestinal Cancer Symposium 2027 (Bericht)
+Onkologie-Update-Seminar Berlin (Bericht)
+ASCO-GU Genitourinary Cancers Symposium 2027 (Bericht)</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="n">
@@ -70940,6 +70947,14 @@
           <t>Hämatoonkologie</t>
         </is>
       </c>
+      <c r="J172" t="inlineStr">
+        <is>
+          <t>67. Kongress der Deutschen Gesellschaft für Pneumologie (DGP) (Bericht)
+ESMO Sarcoma and Rare Cancers Congress 2027 (Bericht)
+DGHO Frühjahrstagung 2025 (Bericht)
+ACUTE LEUKEMIAS XX (ISAL) (Bericht)</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="n">
@@ -70987,7 +71002,11 @@
       </c>
       <c r="J173" t="inlineStr">
         <is>
-          <t>DGS Kongress (Auslage), 17.06.−19.06.2027, Berlin</t>
+          <t>DGS Kongress (Auslage), 17.06.−19.06.2027, Berlin
+20th St. Gallen International Breast Cancer Conference (Bericht)
+53. Annual Meeting of the EBMT (Bericht)
+The 19th International Congress on Myelodysplastic Syndrome (Bericht)
+23. EADO Congress</t>
         </is>
       </c>
     </row>
@@ -71035,6 +71054,12 @@
           <t>Kopf-Hals-Tumoren</t>
         </is>
       </c>
+      <c r="J174" t="inlineStr">
+        <is>
+          <t>DGHNO-KHC-Tagung (Bericht)
+ESMO Breast Cancer Congress 2027 (Bericht)</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="n">
@@ -71080,6 +71105,13 @@
           <t>Uroonkologie</t>
         </is>
       </c>
+      <c r="J175" t="inlineStr">
+        <is>
+          <t>2027 ASCO ANNUAL MEETING of the American Society of Clinical Oncology (Bericht)
+EHA 2027 Congress of the European Hematology Association (Bericht)
+46. Jahreskongress der DGS e.V. 2027 (Bericht)</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="n">
@@ -71127,7 +71159,10 @@
       </c>
       <c r="J176" t="inlineStr">
         <is>
-          <t>DGHO Jahrestagung (Auslage), 08.10.−11.10.2027, Leipzig</t>
+          <t>DGHO Jahrestagung (Auslage), 08.10.−11.10.2027, Leipzig
+19th International Conference on Malignant Lymphoma (ICML 2027) (Bericht)
+ESMO Gynaecological Cancers Congress 2026 (Bericht)
+ESMO Gastrointestinal Cancers Congress 2027 (Bericht)</t>
         </is>
       </c>
     </row>
@@ -71175,6 +71210,13 @@
           <t>Pneumoonkologie</t>
         </is>
       </c>
+      <c r="J177" t="inlineStr">
+        <is>
+          <t>37. Deutscher Hautkrebskongress (ADO 2027) (Bericht)
+World Conference on Lung Cancer (WCLC 2027)  (Bericht)
+79. Jahreskongress der Deutschen Gesellschaft für Urologie (DGU 2027) (Bericht)</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="n">
@@ -71220,6 +71262,11 @@
           <t>Supportivtherapie</t>
         </is>
       </c>
+      <c r="J178" t="inlineStr">
+        <is>
+          <t>DGHO-Jahrestagung 2027 (Bericht)</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="n">
@@ -71265,6 +71312,11 @@
           <t>Allgemeine Onkologie</t>
         </is>
       </c>
+      <c r="J179" t="inlineStr">
+        <is>
+          <t>ESMO Congress 2027 (Bericht)</t>
+        </is>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="n">
@@ -71305,12 +71357,17 @@
           <t>25.01.</t>
         </is>
       </c>
+      <c r="I180" t="inlineStr">
+        <is>
+          <t>Titelthema wird aktuell pro Ausgabe festgelegt</t>
+        </is>
+      </c>
       <c r="J180" t="inlineStr">
         <is>
           <t>DGP Kongress (Auslage), 03.03.–06.03.2027, Köln
-23. AIO-Herbstkongress 2026 (Bericht)
-68th ASH Annual Meeting and Exposition 2026 (ASH 2026) (Bericht)
-48th Annual San Antonio Breast Cancer Symposium (SABCS 2026)</t>
+AIO-Herbstkongress 2026 (Bericht), 19.11.–21.11.2026, Berlin
+ASH Annual Meeting 2026 (Bericht), 12.12.–15.12.2026, New Orleans
+SABCS 2026 (Bericht), 08.12.–11.12.2026, San Antonio</t>
         </is>
       </c>
     </row>
@@ -71353,9 +71410,15 @@
           <t>12.03.</t>
         </is>
       </c>
+      <c r="I181" t="inlineStr">
+        <is>
+          <t>Titelthema wird aktuell pro Ausgabe festgelegt</t>
+        </is>
+      </c>
       <c r="J181" t="inlineStr">
         <is>
-          <t>DCK (Auslage), 21.04.−23.04.2027, München</t>
+          <t>DCK (Auslage), 21.04.−23.04.2027, München
+ASCO-GI Cancers Symposium (Bericht), 21.01.–23.01.2027, San Francisco</t>
         </is>
       </c>
     </row>
@@ -71398,9 +71461,19 @@
           <t>13.05.</t>
         </is>
       </c>
+      <c r="I182" t="inlineStr">
+        <is>
+          <t>Titelthema wird aktuell pro Ausgabe festgelegt</t>
+        </is>
+      </c>
       <c r="J182" t="inlineStr">
         <is>
-          <t>DGS Kongress (Auslage), 17.06.−19.06.2027, Berlin</t>
+          <t>DGS Kongress (Auslage), 17.06.−19.06.2027, Berlin
+GTH Jahrestagung (Bericht), 02.03.–05.03.2027, Hamburg
+ACUTE LEUKEMIAS XX (Bericht), 14.04.–17.03.2027, München
+SGBCC (Bericht), 17.03.–20.03.2027, Wien
+European Lung Cancer Congress (ELCC 2027) (Bericht)
+133. Kongress der Deutschen Gesellschaft für Innere Medizin (Bericht)</t>
         </is>
       </c>
     </row>
@@ -71443,9 +71516,17 @@
           <t>07.07.</t>
         </is>
       </c>
+      <c r="I183" t="inlineStr">
+        <is>
+          <t>Titelthema wird aktuell pro Ausgabe festgelegt</t>
+        </is>
+      </c>
       <c r="J183" t="inlineStr">
         <is>
-          <t>DGT Jahrestagung (Auslage), 09.09.–11.09.2027, Mainz</t>
+          <t>DGT Jahrestagung (Auslage), 09.09.–11.09.2027, Mainz
+23. EADO Congress (Bericht)
+2027 ASCO ANNUAL MEETING of the American Society of Clinical Oncology (Bericht)
+EHA 2027 Congress of the European Hematology Association (Bericht)</t>
         </is>
       </c>
     </row>
@@ -71488,9 +71569,18 @@
           <t>08.09.</t>
         </is>
       </c>
+      <c r="I184" t="inlineStr">
+        <is>
+          <t>Titelthema wird aktuell pro Ausgabe festgelegt</t>
+        </is>
+      </c>
       <c r="J184" t="inlineStr">
         <is>
-          <t>DGHO Jahrestagung (Auslage), 08.11.−11.10.2027, Leipzig</t>
+          <t>DGHO Jahrestagung (Auslage), 08.11.−11.10.2027, Leipzig
+19th International Conference on Malignant Lymphoma (ICML 2027) (Bericht)
+46. Jahreskongress der DGS e.V. 2027 (Bericht)
+15th European Post-Chicago Melanoma/Skin Cancer Meeting 2027 (Bericht)
+ESMO Gastrointestinal Cancers Congress 2027 (Bericht)</t>
         </is>
       </c>
     </row>
@@ -71533,6 +71623,18 @@
           <t>10.11.</t>
         </is>
       </c>
+      <c r="I185" t="inlineStr">
+        <is>
+          <t>Titelthema wird aktuell pro Ausgabe festgelegt</t>
+        </is>
+      </c>
+      <c r="J185" t="inlineStr">
+        <is>
+          <t>SOHO 2027 Annual Meeting  (Bericht)
+World Conference on Lung Cancer (WCLC 2027)
+DGHO-Jahrestagung 2027 (Bericht)</t>
+        </is>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="n">
@@ -71624,7 +71726,10 @@
       </c>
       <c r="J187" t="inlineStr">
         <is>
-          <t>DCK (Auslage), 21.04.−23.04.2027, München</t>
+          <t>DCK (Auslage), 21.04.−23.04.2027, München
+ASCO-GI Gastrointestinal Cancer Symposium 2027 (Bericht)
+Onkologie-Update-Seminar Berlin (Bericht)
+ASCO-GU Genitourinary Cancers Symposium 2027 (Bericht)</t>
         </is>
       </c>
     </row>
@@ -71668,6 +71773,13 @@
 SCHWERPUNKT-THEMA: Lymphome – neue Substanzen, neue Hoffnung (B-Zell-Lymphome, T-Zell-Lymphome, MCL etc.)</t>
         </is>
       </c>
+      <c r="J188" t="inlineStr">
+        <is>
+          <t>67. Kongress der Deutschen Gesellschaft für Pneumologie (DGP) (Bericht)
+DGHO Frühjahrstagung 2025 (Bericht)
+ACUTE LEUKEMIAS XX (ISAL) (Bericht)</t>
+        </is>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="n">
@@ -71711,7 +71823,10 @@
       </c>
       <c r="J189" t="inlineStr">
         <is>
-          <t>DGS Kongress (Auslage), 17.06.−19.06.2027, Berlin</t>
+          <t>DGS Kongress (Auslage), 17.06.−19.06.2027, Berlin
+European Lung Cancer Congress (ELCC 2027) (Bericht)
+23. EADO Congress (Bericht)
+8th European Myeloma Network Meeting (EMN) (Bericht)</t>
         </is>
       </c>
     </row>
@@ -71757,7 +71872,8 @@
       </c>
       <c r="J190" t="inlineStr">
         <is>
-          <t>ASCO Annual Meeting (Bericht), 04.–08.06.2027, Chicago</t>
+          <t>ASCO Annual Meeting (Bericht), 04.–08.06.2027, Chicago
+ESMO Breast Cancer Congress 2027 (Bericht)</t>
         </is>
       </c>
     </row>
@@ -71803,7 +71919,9 @@
       </c>
       <c r="J191" t="inlineStr">
         <is>
-          <t>EHA Congress (Bericht), 13.–17.06.2027, Barcelona</t>
+          <t>EHA Congress (Bericht), 13.–17.06.2027, Barcelona
+ESMO Gynaecological Cancers Congress 2026 (Bericht)
+46. Jahreskongress der DGS e.V. 2027 (Bericht)</t>
         </is>
       </c>
     </row>
@@ -71849,7 +71967,10 @@
       </c>
       <c r="J192" t="inlineStr">
         <is>
-          <t>DGHO Jahrestagung (Auslage), 08.11.−11.10.2027, Leipzig</t>
+          <t>DGHO Jahrestagung (Auslage), 08.11.−11.10.2027, Leipzig
+19th International Conference on Malignant Lymphoma (ICML 2027) (Bericht)
+15th European Post-Chicago Melanoma/Skin Cancer Meeting 2027 (Bericht)
+ESMO Gastrointestinal Cancers Congress 2027 (Bericht)</t>
         </is>
       </c>
     </row>
@@ -71893,6 +72014,13 @@
 SCHWERPUNKT-THEMA: Aktuelles zu Diagnostik und Therapie des kolorektalen Karzinoms</t>
         </is>
       </c>
+      <c r="J193" t="inlineStr">
+        <is>
+          <t>SOHO 2027 Annual Meeting  (Bericht)
+37. Deutscher Hautkrebskongress (ADO 2027) (Bericht)
+World Conference on Lung Cancer (WCLC 2027) (Bericht)</t>
+        </is>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="n">
@@ -71936,7 +72064,8 @@
       </c>
       <c r="J194" t="inlineStr">
         <is>
-          <t>DGHO Jahrestagung (Bericht), 08.11.−11.10.2027, Leipzig</t>
+          <t>DGHO Jahrestagung (Bericht), 08.11.−11.10.2027, Leipzig
+79. Jahreskongress der Deutschen Gesellschaft für Urologie (DGU 2027) (Bericht)</t>
         </is>
       </c>
     </row>
@@ -71980,6 +72109,11 @@
 SCHWERPUNKT-THEMA: Multimodale Ansätze beim Prostatakarzinom</t>
         </is>
       </c>
+      <c r="J195" t="inlineStr">
+        <is>
+          <t>ESMO Congress 2027 (Bericht)</t>
+        </is>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="n">
@@ -75691,6 +75825,11 @@
       <c r="D320" t="inlineStr">
         <is>
           <t>Februar</t>
+        </is>
+      </c>
+      <c r="J320" t="inlineStr">
+        <is>
+          <t>ESMO Congress 2027 (Bericht)</t>
         </is>
       </c>
     </row>

--- a/Angebotsdaten.xlsx
+++ b/Angebotsdaten.xlsx
@@ -71472,8 +71472,8 @@
 GTH Jahrestagung (Bericht), 02.03.–05.03.2027, Hamburg
 ACUTE LEUKEMIAS XX (Bericht), 14.04.–17.03.2027, München
 SGBCC (Bericht), 17.03.–20.03.2027, Wien
-European Lung Cancer Congress (ELCC 2027) (Bericht)
-133. Kongress der Deutschen Gesellschaft für Innere Medizin (Bericht)</t>
+ELCC (Bericht), 17.03.–20.03.2027, München
+DGIM Kongress (Bericht), 10.04.–13.04.2027, Wiesbaden</t>
         </is>
       </c>
     </row>
@@ -71524,9 +71524,9 @@
       <c r="J183" t="inlineStr">
         <is>
           <t>DGT Jahrestagung (Auslage), 09.09.–11.09.2027, Mainz
-23. EADO Congress (Bericht)
-2027 ASCO ANNUAL MEETING of the American Society of Clinical Oncology (Bericht)
-EHA 2027 Congress of the European Hematology Association (Bericht)</t>
+EADO Congress (Bericht), 15.04.–17.04.2027, Wien
+ASCO Annual Meeting (Bericht), 04.06.–08.06.2027, Chicago
+EHA Congress (Bericht), 10.06.–13.06.2027, Barcelona</t>
         </is>
       </c>
     </row>
@@ -71577,10 +71577,10 @@
       <c r="J184" t="inlineStr">
         <is>
           <t>DGHO Jahrestagung (Auslage), 08.11.−11.10.2027, Leipzig
-19th International Conference on Malignant Lymphoma (ICML 2027) (Bericht)
-46. Jahreskongress der DGS e.V. 2027 (Bericht)
-15th European Post-Chicago Melanoma/Skin Cancer Meeting 2027 (Bericht)
-ESMO Gastrointestinal Cancers Congress 2027 (Bericht)</t>
+ICML (Bericht), 15.06.–19.06.2027, Lugano
+DGS Jahreskongress (Bericht), 17.07.–19.06.2027, Berlin
+EPCM (Bericht), 08.09.–11.09.2027, Hamburg
+ESMO-GI Cancers Congress (Bericht), 30.06.–03.07.2027, Barcelona</t>
         </is>
       </c>
     </row>
@@ -71630,9 +71630,9 @@
       </c>
       <c r="J185" t="inlineStr">
         <is>
-          <t>SOHO 2027 Annual Meeting  (Bericht)
-World Conference on Lung Cancer (WCLC 2027)
-DGHO-Jahrestagung 2027 (Bericht)</t>
+          <t>SOHO Annual Meeting  (Bericht), 25.08.–28.08.2027, Houston
+WCLC (Bericht), 11.09.–14.09.2027, Denver
+DGHO Jahrestagung (Bericht), 08.10.–11.10.2027, Leipzig</t>
         </is>
       </c>
     </row>

--- a/Angebotsdaten.xlsx
+++ b/Angebotsdaten.xlsx
@@ -70929,7 +70929,7 @@
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>25.03.</t>
+          <t>24.03.</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
@@ -71087,7 +71087,7 @@
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>02.07.</t>
+          <t>01.07.</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
@@ -71503,7 +71503,7 @@
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>25.06.</t>
+          <t>24.06.</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
@@ -71556,7 +71556,7 @@
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>27.08.</t>
+          <t>26.08.</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
@@ -72519,7 +72519,7 @@
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>26.01.</t>
+          <t>25.01.</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
@@ -72614,7 +72614,7 @@
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>26.05.</t>
+          <t>25.05.</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">

--- a/Angebotsdaten.xlsx
+++ b/Angebotsdaten.xlsx
@@ -65560,7 +65560,7 @@
       <c r="I48" t="inlineStr">
         <is>
           <t>TOP-THEMA: Morbus Waldenström – Wo stehen wir?
-SCHWERPUNKT-THEMA: Das fortgeschrittene malignes Melanom auf dem Weg zu einer chronische Erkrankung (Therapie und Nachsorge)</t>
+SCHWERPUNKT-THEMA: Das fortgeschrittene maligne Melanom auf dem Weg zu einer chronische Erkrankung (Therapie und Nachsorge)</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -71670,6 +71670,11 @@
           <t>27.01.</t>
         </is>
       </c>
+      <c r="H186" t="inlineStr">
+        <is>
+          <t>29.01.</t>
+        </is>
+      </c>
       <c r="I186" t="inlineStr">
         <is>
           <t>TOP-THEMA: Chronische Graft-versus-Host-Erkrankung (cGvHD) – Neue Optionen abseits von Kortikosteroiden
@@ -71716,6 +71721,11 @@
       <c r="G187" t="inlineStr">
         <is>
           <t>10.03.</t>
+        </is>
+      </c>
+      <c r="H187" t="inlineStr">
+        <is>
+          <t>12.03.</t>
         </is>
       </c>
       <c r="I187" t="inlineStr">
@@ -71767,6 +71777,11 @@
           <t>13.04.</t>
         </is>
       </c>
+      <c r="H188" t="inlineStr">
+        <is>
+          <t>15.04.</t>
+        </is>
+      </c>
       <c r="I188" t="inlineStr">
         <is>
           <t>TOP-THEMA: Pankreaskarzinom – Auf dem Weg zu kurativen Konzepten?
@@ -71813,6 +71828,11 @@
       <c r="G189" t="inlineStr">
         <is>
           <t>11.05.</t>
+        </is>
+      </c>
+      <c r="H189" t="inlineStr">
+        <is>
+          <t>13.05.</t>
         </is>
       </c>
       <c r="I189" t="inlineStr">
@@ -71864,6 +71884,11 @@
           <t>16.06.</t>
         </is>
       </c>
+      <c r="H190" t="inlineStr">
+        <is>
+          <t>18.06.</t>
+        </is>
+      </c>
       <c r="I190" t="inlineStr">
         <is>
           <t>TOP-THEMA: Wirtschaft / Gesundheitspolitik
@@ -71911,6 +71936,11 @@
           <t>14.07.</t>
         </is>
       </c>
+      <c r="H191" t="inlineStr">
+        <is>
+          <t>16.07.</t>
+        </is>
+      </c>
       <c r="I191" t="inlineStr">
         <is>
           <t>TOP-THEMA: Wirtschaft / Gesundheitspolitik
@@ -71957,6 +71987,11 @@
       <c r="G192" t="inlineStr">
         <is>
           <t>01.09.</t>
+        </is>
+      </c>
+      <c r="H192" t="inlineStr">
+        <is>
+          <t>03.09.</t>
         </is>
       </c>
       <c r="I192" t="inlineStr">
@@ -72008,6 +72043,11 @@
           <t>29.09.</t>
         </is>
       </c>
+      <c r="H193" t="inlineStr">
+        <is>
+          <t>01.10.</t>
+        </is>
+      </c>
       <c r="I193" t="inlineStr">
         <is>
           <t>TOP-THEMA: Präzisionsonkologie beim Brustkrebs – Deeskalation und Patientenindividualisierung
@@ -72056,6 +72096,11 @@
           <t>02.11.</t>
         </is>
       </c>
+      <c r="H194" t="inlineStr">
+        <is>
+          <t>04.11.</t>
+        </is>
+      </c>
       <c r="I194" t="inlineStr">
         <is>
           <t>TOP-THEMA: Wirtschaft / Gesundheitspolitik
@@ -72101,6 +72146,11 @@
       <c r="G195" t="inlineStr">
         <is>
           <t>01.12.</t>
+        </is>
+      </c>
+      <c r="H195" t="inlineStr">
+        <is>
+          <t>03.12.</t>
         </is>
       </c>
       <c r="I195" t="inlineStr">

--- a/Angebotsdaten.xlsx
+++ b/Angebotsdaten.xlsx
@@ -66061,6 +66061,11 @@
           <t>12.01.</t>
         </is>
       </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>Akutmedizin</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -66101,6 +66106,11 @@
           <t>05.02.</t>
         </is>
       </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>Interdisziplinäre konservative Tumortherapie</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -66141,6 +66151,11 @@
           <t>02.03.</t>
         </is>
       </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>Urothelkarzinom</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -66181,6 +66196,11 @@
           <t>26.03.</t>
         </is>
       </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>Prothetik</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -66221,6 +66241,11 @@
           <t>28.04.</t>
         </is>
       </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>Praxisrelevantes aus den urologischen Leitlinien</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -66261,6 +66286,11 @@
           <t>29.05.</t>
         </is>
       </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>KI in der Urologie</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -66301,6 +66331,11 @@
           <t>24.06.</t>
         </is>
       </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>Indikation / Deeskalation</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -66341,6 +66376,11 @@
           <t>23.07.</t>
         </is>
       </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>Berufspolitik</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -66381,9 +66421,14 @@
           <t>20.08.</t>
         </is>
       </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>Kongressheft DGU</t>
+        </is>
+      </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>Kongressausgabe zum 78. Kongress der Deutschen Gesellschaft für Urologie, 16.09.−19.09.2026, Düsseldorf</t>
+          <t>DGU Kongress, 16.09.−19.09.2026, Düsseldorf</t>
         </is>
       </c>
     </row>
@@ -66426,6 +66471,11 @@
           <t>30.09.</t>
         </is>
       </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>Urogeriatrie</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -66466,6 +66516,11 @@
           <t>28.10.</t>
         </is>
       </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>Transgender Medizin</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -66506,6 +66561,11 @@
           <t>27.11.</t>
         </is>
       </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>Traumatologie</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -66546,6 +66606,11 @@
           <t>17.12.2025</t>
         </is>
       </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>Endourologie</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -66586,6 +66651,11 @@
           <t>26.01.</t>
         </is>
       </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>Urologische Früherkennung in der Real World</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -66626,6 +66696,11 @@
           <t>23.02.</t>
         </is>
       </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>Urothelkarzinom</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -66666,6 +66741,11 @@
           <t>26.03.</t>
         </is>
       </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>Trans-Chirurgie</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -66706,6 +66786,11 @@
           <t>22.04.</t>
         </is>
       </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>Tagesaktuelles aus der Niederlassung</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -66746,6 +66831,11 @@
           <t>22.05.</t>
         </is>
       </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>Diagnostik in der funktionellen Urologie</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -66786,6 +66876,11 @@
           <t>29.06.</t>
         </is>
       </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>Hodenkarzinom</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -66826,9 +66921,14 @@
           <t>24.08.</t>
         </is>
       </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>Junge Sterne</t>
+        </is>
+      </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>Kongressausgabe zum 78. Kongress der Deutschen Gesellschaft für Urologie, 16.09.−19.09.2026, Düsseldorf</t>
+          <t>DGU Kongress, 16.09.−19.09.2026, Düsseldorf</t>
         </is>
       </c>
     </row>
@@ -66871,6 +66971,11 @@
           <t>25.09.</t>
         </is>
       </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>Digitale Urologie</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -66911,6 +67016,11 @@
           <t>26.10.</t>
         </is>
       </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>Post-Kongress-Ausgabe</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -66951,6 +67061,11 @@
           <t>23.11.</t>
         </is>
       </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>Hormone</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -67026,6 +67141,11 @@
           <t>21.01.</t>
         </is>
       </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>Husten</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -67066,9 +67186,15 @@
           <t>18.02.</t>
         </is>
       </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>Pleuraerkrankungen / Erkrankungen der
+Thoraxwand</t>
+        </is>
+      </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>66. Kongress der Deutschen Gesellschaft für Pneumologie, 18.–21.03.2026, München</t>
+          <t>DGP Kongress, 18.–21.03.2026, München</t>
         </is>
       </c>
     </row>
@@ -67111,6 +67237,11 @@
           <t>22.04.</t>
         </is>
       </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>Tuberkulose und nichttuberkulöse Mykobakterien</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -67151,6 +67282,11 @@
           <t>19.06.</t>
         </is>
       </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>Cannabis, Nikotine, Shisha, e-Zigarette : Was passiert in der Lunge?</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -67191,6 +67327,12 @@
           <t>20.08.</t>
         </is>
       </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>Neues zum Lungenkarzinom vom Screening bis
+fortgeschrittenes Stadium</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -67231,6 +67373,11 @@
           <t>22.10.</t>
         </is>
       </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>COPD: Von Prä-COPD bis zum Endstadium</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -67271,9 +67418,15 @@
           <t>17.02.</t>
         </is>
       </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>Pulmonale Sarkoidose
+Differenzialdiagnostik granulomatöser Veränderungen in der Lunge</t>
+        </is>
+      </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>66. Kongress der Deutschen Gesellschaft für Pneumologie, 18.–21.03.2026, München</t>
+          <t>DGP Kongress, 18.–21.03.2026, München</t>
         </is>
       </c>
     </row>
@@ -67316,6 +67469,12 @@
           <t>14.04.</t>
         </is>
       </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>IPF und PPF
+Neue deutsche S2k-Leitlinie zur exogen allergischen Alveolitis</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -67356,6 +67515,13 @@
           <t>16.06.</t>
         </is>
       </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>Moderne Therapie bei zystischer Fibrose
+Bronchiektasen
+Therapie bei Non-CF-Bronchiektasen</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -67396,6 +67562,13 @@
           <t>25.08.</t>
         </is>
       </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>Target-Therapie beim Bronchialkarzinom
+Nebenwirkungsmanagement
+Lungenkrebsscreening</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -67436,6 +67609,13 @@
           <t>15.10.</t>
         </is>
       </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>Nicht typische Mykobakteriose
+Latente Tuberkulose
+Neue Medikamente in der Tuberkulosetherapie</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -67476,6 +67656,12 @@
           <t>01.12.</t>
         </is>
       </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>Digitale Lösungsansätze in der Pneumologie
+Revolution in der Bronchoskopie: Robotik, Navigationsverfahren</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -67766,6 +67952,11 @@
           <t>04.02.</t>
         </is>
       </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>Hypertonie</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -67806,6 +67997,11 @@
           <t>09.03.</t>
         </is>
       </c>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>Kardiologie</t>
+        </is>
+      </c>
       <c r="J114" t="inlineStr">
         <is>
           <t>92. Jahrestagung der Deutschen Gesellschaft für Kardiologie – Herz- und Kreislaufforschung, 08.–11.04.2026, Mannheim</t>
@@ -67851,6 +68047,11 @@
           <t>27.05.</t>
         </is>
       </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>Adipositas / Diabetes</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -67891,6 +68092,11 @@
           <t>31.08.</t>
         </is>
       </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>Kardiologie</t>
+        </is>
+      </c>
       <c r="J116" t="inlineStr">
         <is>
           <t>Kongressausgabe zu den DGK-Herztagen, 24.–26.09.2026, Hamburg</t>
@@ -67936,6 +68142,11 @@
           <t>08.10.</t>
         </is>
       </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>Neurologie</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -67976,6 +68187,11 @@
           <t>27.11.</t>
         </is>
       </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>Angiologie / Lipidologie</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -68341,6 +68557,11 @@
           <t>28.01.</t>
         </is>
       </c>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>ESC-Leitlinien 2025</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
@@ -68381,6 +68602,11 @@
           <t>11.03.</t>
         </is>
       </c>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>Kongressheft DGK</t>
+        </is>
+      </c>
       <c r="J129" t="inlineStr">
         <is>
           <t>92. Jahrestagung der Deutschen Gesellschaft für Kardiologie – Herz- und Kreislaufforschung, 08.–11.04.2026, Mannheim</t>
@@ -68426,6 +68652,11 @@
           <t>01.06.</t>
         </is>
       </c>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>Herzklappen (insbes. AV-Klappen)</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
@@ -68466,6 +68697,11 @@
           <t>05.08.</t>
         </is>
       </c>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>Umweltfaktoren &amp; Kardiologie (Lärm, Feinstoffpartikel, Hitze…)</t>
+        </is>
+      </c>
       <c r="J131" t="inlineStr">
         <is>
           <t>Kongressausgabe zu den DGK-Herztagen, 24.–26.09.2026, Hamburg</t>
@@ -68511,6 +68747,11 @@
           <t>30.09.</t>
         </is>
       </c>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>Kardiomyopathien</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
@@ -68549,6 +68790,12 @@
       <c r="H133" t="inlineStr">
         <is>
           <t>25.11.</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>Echokardiografie (Guiding, KI,
+Aortenstenose…)</t>
         </is>
       </c>
     </row>
@@ -72311,6 +72558,11 @@
           <t>Februar</t>
         </is>
       </c>
+      <c r="I211" t="inlineStr">
+        <is>
+          <t>Hypertonie</t>
+        </is>
+      </c>
     </row>
     <row r="212">
       <c r="A212" t="n">
@@ -72331,6 +72583,11 @@
           <t>März</t>
         </is>
       </c>
+      <c r="I212" t="inlineStr">
+        <is>
+          <t>Kardiologie</t>
+        </is>
+      </c>
     </row>
     <row r="213">
       <c r="A213" t="n">
@@ -72351,6 +72608,11 @@
           <t>Juni</t>
         </is>
       </c>
+      <c r="I213" t="inlineStr">
+        <is>
+          <t>Adipositas / Diabetes</t>
+        </is>
+      </c>
     </row>
     <row r="214">
       <c r="A214" t="n">
@@ -72371,6 +72633,11 @@
           <t>September</t>
         </is>
       </c>
+      <c r="I214" t="inlineStr">
+        <is>
+          <t>Kardiologie</t>
+        </is>
+      </c>
     </row>
     <row r="215">
       <c r="A215" t="n">
@@ -72391,6 +72658,11 @@
           <t>Oktober</t>
         </is>
       </c>
+      <c r="I215" t="inlineStr">
+        <is>
+          <t>Neurologie</t>
+        </is>
+      </c>
     </row>
     <row r="216">
       <c r="A216" t="n">
@@ -72411,6 +72683,11 @@
           <t>Dezember</t>
         </is>
       </c>
+      <c r="I216" t="inlineStr">
+        <is>
+          <t>Angiologie / Lipidologie</t>
+        </is>
+      </c>
     </row>
     <row r="217">
       <c r="A217" t="n">
@@ -72451,6 +72728,12 @@
           <t>27.01.</t>
         </is>
       </c>
+      <c r="I217" t="inlineStr">
+        <is>
+          <t>ESC-Leitlinien 2026
+CME: Lungenembolie</t>
+        </is>
+      </c>
     </row>
     <row r="218">
       <c r="A218" t="n">
@@ -72491,6 +72774,12 @@
           <t>03.03.</t>
         </is>
       </c>
+      <c r="I218" t="inlineStr">
+        <is>
+          <t>Kongressheft DGK
+CME: Myokarditis</t>
+        </is>
+      </c>
       <c r="J218" t="inlineStr">
         <is>
           <t>DGK Kongressausgabe, 31.03.-03.04.2027, Mannheim</t>
@@ -72536,6 +72825,12 @@
           <t>02.06.</t>
         </is>
       </c>
+      <c r="I219" t="inlineStr">
+        <is>
+          <t>Echokardiografie (Guiding, KI, Aortenstenose…)
+CME: Fettstoffwechselstörungen</t>
+        </is>
+      </c>
     </row>
     <row r="220">
       <c r="A220" t="n">
@@ -72576,6 +72871,12 @@
           <t>04.08.</t>
         </is>
       </c>
+      <c r="I220" t="inlineStr">
+        <is>
+          <t>Herz &amp; Systemerkrankungen (Rheuma, Amyloidose, etc.)
+CME: Psychokardiologie</t>
+        </is>
+      </c>
       <c r="J220" t="inlineStr">
         <is>
           <t>Kongressausgabe zu den DGK Herztagen, Termin noch offen</t>
@@ -72621,6 +72922,12 @@
           <t>29.09.</t>
         </is>
       </c>
+      <c r="I221" t="inlineStr">
+        <is>
+          <t>Herz &amp; Hirn
+CME: Kardiomyopathien</t>
+        </is>
+      </c>
     </row>
     <row r="222">
       <c r="A222" t="n">
@@ -72661,6 +72968,12 @@
           <t>01.12.</t>
         </is>
       </c>
+      <c r="I222" t="inlineStr">
+        <is>
+          <t>Gendermedizin in der Kardiologie
+CME: Kardiogener Schlaganfall</t>
+        </is>
+      </c>
     </row>
     <row r="223">
       <c r="A223" t="n">
@@ -74126,9 +74439,14 @@
           <t>21.01.</t>
         </is>
       </c>
+      <c r="I261" t="inlineStr">
+        <is>
+          <t>Pädiatrische Pneumologie</t>
+        </is>
+      </c>
       <c r="J261" t="inlineStr">
         <is>
-          <t>DGPKongress (Auslage), 03.03.–06.03.2027, Köln</t>
+          <t>DGP Kongress (Auslage), 03.03.–06.03.2027, Köln</t>
         </is>
       </c>
     </row>
@@ -74171,6 +74489,11 @@
           <t>18.02.</t>
         </is>
       </c>
+      <c r="I262" t="inlineStr">
+        <is>
+          <t>Asthma</t>
+        </is>
+      </c>
     </row>
     <row r="263">
       <c r="A263" t="n">
@@ -74211,6 +74534,11 @@
           <t>22.04.</t>
         </is>
       </c>
+      <c r="I263" t="inlineStr">
+        <is>
+          <t>Klimawandel und hohe Temperaturen</t>
+        </is>
+      </c>
     </row>
     <row r="264">
       <c r="A264" t="n">
@@ -74251,6 +74579,11 @@
           <t>21.06.</t>
         </is>
       </c>
+      <c r="I264" t="inlineStr">
+        <is>
+          <t>KI und Digitalisierung</t>
+        </is>
+      </c>
     </row>
     <row r="265">
       <c r="A265" t="n">
@@ -74291,6 +74624,11 @@
           <t>20.08.</t>
         </is>
       </c>
+      <c r="I265" t="inlineStr">
+        <is>
+          <t>Bio-Marker</t>
+        </is>
+      </c>
     </row>
     <row r="266">
       <c r="A266" t="n">
@@ -74329,6 +74667,12 @@
       <c r="H266" t="inlineStr">
         <is>
           <t>22.10.</t>
+        </is>
+      </c>
+      <c r="I266" t="inlineStr">
+        <is>
+          <t>Neue Leitlinie zu Diagnostik und Therapie in
+Atemmuskuläre</t>
         </is>
       </c>
     </row>
